--- a/AAII_Financials/Quarterly/VLDX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VLDX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>VLDX</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -756,10 +756,10 @@
         <v>22300</v>
       </c>
       <c r="H9" s="3">
-        <v>44400</v>
+        <v>22600</v>
       </c>
       <c r="I9" s="3">
-        <v>47600</v>
+        <v>24200</v>
       </c>
       <c r="J9" s="3">
         <v>28000</v>
@@ -779,16 +779,16 @@
         <v>-2800</v>
       </c>
       <c r="F10" s="3">
-        <v>-33600</v>
+        <v>-33700</v>
       </c>
       <c r="G10" s="3">
         <v>1500</v>
       </c>
       <c r="H10" s="3">
-        <v>-19300</v>
+        <v>2500</v>
       </c>
       <c r="I10" s="3">
-        <v>-20900</v>
+        <v>2500</v>
       </c>
       <c r="J10" s="3">
         <v>-300</v>
@@ -872,26 +872,26 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>400</v>
       </c>
       <c r="F14" s="3">
-        <v>19200</v>
+        <v>2600</v>
       </c>
       <c r="G14" s="3">
-        <v>300</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
+        <v>-6900</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>9700</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -902,25 +902,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -947,10 +947,10 @@
         <v>31200</v>
       </c>
       <c r="F17" s="3">
-        <v>79100</v>
+        <v>59900</v>
       </c>
       <c r="G17" s="3">
-        <v>49300</v>
+        <v>49000</v>
       </c>
       <c r="H17" s="3">
         <v>50800</v>
@@ -970,25 +970,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-20600</v>
+        <v>-20500</v>
       </c>
       <c r="E18" s="3">
-        <v>-21400</v>
+        <v>-21500</v>
       </c>
       <c r="F18" s="3">
-        <v>-77400</v>
+        <v>-58200</v>
       </c>
       <c r="G18" s="3">
-        <v>-25500</v>
+        <v>-25200</v>
       </c>
       <c r="H18" s="3">
         <v>-25700</v>
       </c>
       <c r="I18" s="3">
-        <v>-24200</v>
+        <v>-24300</v>
       </c>
       <c r="J18" s="3">
-        <v>-24000</v>
+        <v>-23900</v>
       </c>
       <c r="K18" s="3">
         <v>-28000</v>
@@ -1012,25 +1012,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>25900</v>
+        <v>-24000</v>
       </c>
       <c r="E20" s="3">
-        <v>-3000</v>
+        <v>2500</v>
       </c>
       <c r="F20" s="3">
-        <v>27100</v>
+        <v>-10500</v>
       </c>
       <c r="G20" s="3">
-        <v>9200</v>
+        <v>-2000</v>
       </c>
       <c r="H20" s="3">
-        <v>2900</v>
+        <v>-1000</v>
       </c>
       <c r="I20" s="3">
-        <v>-11900</v>
+        <v>2200</v>
       </c>
       <c r="J20" s="3">
-        <v>44500</v>
+        <v>-8500</v>
       </c>
       <c r="K20" s="3">
         <v>-47100</v>
@@ -1041,25 +1041,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3400</v>
+        <v>4800</v>
       </c>
       <c r="E21" s="3">
-        <v>-19800</v>
+        <v>-19400</v>
       </c>
       <c r="F21" s="3">
-        <v>-45500</v>
+        <v>-42900</v>
       </c>
       <c r="G21" s="3">
-        <v>-14800</v>
+        <v>-21700</v>
       </c>
       <c r="H21" s="3">
-        <v>-21400</v>
+        <v>-23300</v>
       </c>
       <c r="I21" s="3">
-        <v>-34500</v>
+        <v>-24900</v>
       </c>
       <c r="J21" s="3">
-        <v>22500</v>
+        <v>-13400</v>
       </c>
       <c r="K21" s="3">
         <v>-73800</v>
@@ -1133,20 +1133,20 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1360,25 +1360,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-25900</v>
+        <v>24000</v>
       </c>
       <c r="E32" s="3">
-        <v>3000</v>
+        <v>-2500</v>
       </c>
       <c r="F32" s="3">
-        <v>-27100</v>
+        <v>10500</v>
       </c>
       <c r="G32" s="3">
-        <v>-9200</v>
+        <v>2000</v>
       </c>
       <c r="H32" s="3">
-        <v>-2900</v>
+        <v>1000</v>
       </c>
       <c r="I32" s="3">
-        <v>11900</v>
+        <v>-2200</v>
       </c>
       <c r="J32" s="3">
-        <v>-44500</v>
+        <v>8500</v>
       </c>
       <c r="K32" s="3">
         <v>47100</v>
@@ -1652,25 +1652,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2300</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
-        <v>3100</v>
+        <v>200</v>
       </c>
       <c r="F45" s="3">
-        <v>4000</v>
+        <v>1300</v>
       </c>
       <c r="G45" s="3">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="H45" s="3">
-        <v>2900</v>
+        <v>900</v>
       </c>
       <c r="I45" s="3">
-        <v>4600</v>
+        <v>1800</v>
       </c>
       <c r="J45" s="3">
-        <v>5500</v>
+        <v>2200</v>
       </c>
       <c r="K45" s="3">
         <v>4600</v>
@@ -1709,11 +1709,11 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>4900</v>
-      </c>
-      <c r="E47" s="3">
-        <v>4800</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>10</v>
@@ -1757,7 +1757,7 @@
         <v>38600</v>
       </c>
       <c r="J48" s="3">
-        <v>28900</v>
+        <v>42400</v>
       </c>
       <c r="K48" s="3">
         <v>27300</v>
@@ -1864,16 +1864,16 @@
         <v>2000</v>
       </c>
       <c r="G52" s="3">
-        <v>10200</v>
+        <v>4400</v>
       </c>
       <c r="H52" s="3">
-        <v>10800</v>
+        <v>4500</v>
       </c>
       <c r="I52" s="3">
-        <v>10200</v>
+        <v>3900</v>
       </c>
       <c r="J52" s="3">
-        <v>22700</v>
+        <v>3200</v>
       </c>
       <c r="K52" s="3">
         <v>20100</v>
@@ -1997,25 +1997,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>24700</v>
+        <v>26600</v>
       </c>
       <c r="E58" s="3">
-        <v>34400</v>
+        <v>36400</v>
       </c>
       <c r="F58" s="3">
-        <v>21300</v>
+        <v>23500</v>
       </c>
       <c r="G58" s="3">
-        <v>52300</v>
+        <v>54500</v>
       </c>
       <c r="H58" s="3">
-        <v>3000</v>
+        <v>5300</v>
       </c>
       <c r="I58" s="3">
-        <v>2800</v>
+        <v>5100</v>
       </c>
       <c r="J58" s="3">
-        <v>2800</v>
+        <v>5200</v>
       </c>
       <c r="K58" s="3">
         <v>2000</v>
@@ -2026,25 +2026,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9800</v>
+        <v>4100</v>
       </c>
       <c r="E59" s="3">
-        <v>10800</v>
+        <v>4700</v>
       </c>
       <c r="F59" s="3">
-        <v>11500</v>
+        <v>5100</v>
       </c>
       <c r="G59" s="3">
-        <v>33600</v>
+        <v>22400</v>
       </c>
       <c r="H59" s="3">
-        <v>15100</v>
+        <v>5800</v>
       </c>
       <c r="I59" s="3">
-        <v>24400</v>
+        <v>10600</v>
       </c>
       <c r="J59" s="3">
-        <v>31000</v>
+        <v>15200</v>
       </c>
       <c r="K59" s="3">
         <v>45700</v>
@@ -2084,25 +2084,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>9300</v>
       </c>
       <c r="E61" s="3">
-        <v>2200</v>
+        <v>11800</v>
       </c>
       <c r="F61" s="3">
-        <v>12100</v>
+        <v>22100</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>10600</v>
       </c>
       <c r="H61" s="3">
-        <v>19400</v>
+        <v>30400</v>
       </c>
       <c r="I61" s="3">
-        <v>9800</v>
+        <v>21400</v>
       </c>
       <c r="J61" s="3">
-        <v>5400</v>
+        <v>17600</v>
       </c>
       <c r="K61" s="3">
         <v>4400</v>
@@ -2113,25 +2113,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>15800</v>
+        <v>6600</v>
       </c>
       <c r="E62" s="3">
-        <v>27600</v>
+        <v>18100</v>
       </c>
       <c r="F62" s="3">
-        <v>24600</v>
+        <v>14700</v>
       </c>
       <c r="G62" s="3">
-        <v>28000</v>
+        <v>17600</v>
       </c>
       <c r="H62" s="3">
-        <v>41100</v>
+        <v>30100</v>
       </c>
       <c r="I62" s="3">
-        <v>44300</v>
+        <v>32700</v>
       </c>
       <c r="J62" s="3">
-        <v>32800</v>
+        <v>20600</v>
       </c>
       <c r="K62" s="3">
         <v>78400</v>
@@ -2637,25 +2637,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>-1900</v>
+        <v>1400</v>
       </c>
       <c r="E83" s="3">
-        <v>4600</v>
+        <v>1600</v>
       </c>
       <c r="F83" s="3">
-        <v>4800</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="H83" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="I83" s="3">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="K83" s="3">
         <v>1200</v>
@@ -2859,10 +2859,10 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="G91" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="H91" s="3">
         <v>-3800</v>
@@ -2981,26 +2981,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3133,10 +3133,10 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
